--- a/data/trans_orig/P41E_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023</t>
+          <t>Población según si con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023 (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>12572</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13983</t>
+          <t>13230</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9365</t>
+          <t>9814</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21410</t>
+          <t>21710</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15680</t>
+          <t>16349</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10651</t>
+          <t>10682</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22556</t>
+          <t>22783</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21079</t>
+          <t>21876</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40038</t>
+          <t>39898</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14198</t>
+          <t>14134</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27350</t>
+          <t>26953</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39678</t>
+          <t>39859</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>62027</t>
+          <t>60894</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69268</t>
+          <t>69993</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97270</t>
+          <t>100283</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58838</t>
+          <t>59419</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80839</t>
+          <t>81990</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>134665</t>
+          <t>135085</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>173151</t>
+          <t>172342</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>135497</t>
+          <t>133369</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>167074</t>
+          <t>166601</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>103731</t>
+          <t>102681</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>127045</t>
+          <t>128021</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>244301</t>
+          <t>245814</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>285719</t>
+          <t>286274</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,33%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9056</t>
+          <t>8561</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22756</t>
+          <t>22347</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15051</t>
+          <t>13713</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15888</t>
+          <t>15846</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32780</t>
+          <t>31662</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17032</t>
+          <t>16941</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8148</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>8710</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21438</t>
+          <t>21969</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15263</t>
+          <t>15808</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31916</t>
+          <t>32481</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>12365</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25607</t>
+          <t>26269</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32262</t>
+          <t>32321</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>53544</t>
+          <t>53438</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66561</t>
+          <t>66457</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95147</t>
+          <t>95219</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54805</t>
+          <t>53856</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76476</t>
+          <t>76669</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127708</t>
+          <t>126868</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162871</t>
+          <t>162311</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,09%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92104</t>
+          <t>92092</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>124031</t>
+          <t>122555</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>83380</t>
+          <t>82591</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>106832</t>
+          <t>106635</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>182134</t>
+          <t>184986</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>220141</t>
+          <t>223078</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>52,35%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46395</t>
+          <t>47302</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15651</t>
+          <t>15846</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10836</t>
+          <t>11655</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61433</t>
+          <t>60554</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27821</t>
+          <t>27263</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30815</t>
+          <t>31619</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50904</t>
+          <t>51285</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12869</t>
+          <t>12385</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57017</t>
+          <t>61415</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23442</t>
+          <t>25519</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>162209</t>
+          <t>166707</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22361</t>
+          <t>22171</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35778</t>
+          <t>35481</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38144</t>
+          <t>38396</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>193214</t>
+          <t>194810</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>197075</t>
+          <t>197058</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>432781</t>
+          <t>430155</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23527</t>
+          <t>23056</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36690</t>
+          <t>36514</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>224925</t>
+          <t>219086</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>484857</t>
+          <t>485912</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,74%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25254</t>
+          <t>24391</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45388</t>
+          <t>44665</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31338</t>
+          <t>30626</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27148</t>
+          <t>25177</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69374</t>
+          <t>68416</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19062</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36293</t>
+          <t>35868</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19652</t>
+          <t>20988</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20530</t>
+          <t>17644</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52118</t>
+          <t>52586</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>37620</t>
+          <t>37383</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>63095</t>
+          <t>62886</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11347</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53602</t>
+          <t>51804</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>43722</t>
+          <t>39232</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>103776</t>
+          <t>105357</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>113246</t>
+          <t>114524</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>153547</t>
+          <t>152641</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46368</t>
+          <t>38334</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>175338</t>
+          <t>173571</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>139968</t>
+          <t>128929</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>313164</t>
+          <t>309829</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>209043</t>
+          <t>208987</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>250540</t>
+          <t>251507</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>294463</t>
+          <t>294416</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>490814</t>
+          <t>502284</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>514922</t>
+          <t>517813</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>800023</t>
+          <t>819656</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>79,24%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18905</t>
+          <t>18694</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>35259</t>
+          <t>34320</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>36384</t>
+          <t>37134</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>55093</t>
+          <t>55436</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>59640</t>
+          <t>59828</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>84490</t>
+          <t>84315</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14037</t>
+          <t>13481</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10140</t>
+          <t>10382</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21642</t>
+          <t>21454</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>16041</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31054</t>
+          <t>31141</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10893</t>
+          <t>10926</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25050</t>
+          <t>24568</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>34297</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>53524</t>
+          <t>52386</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>49585</t>
+          <t>49667</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>72557</t>
+          <t>73496</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>66422</t>
+          <t>65951</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>95823</t>
+          <t>97314</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>83515</t>
+          <t>83681</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>109853</t>
+          <t>109409</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>157159</t>
+          <t>157430</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>199640</t>
+          <t>197666</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,04%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>78225</t>
+          <t>77130</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>110674</t>
+          <t>110748</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>122115</t>
+          <t>121765</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>151894</t>
+          <t>151235</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>209026</t>
+          <t>210499</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>255086</t>
+          <t>254311</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,09%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>688</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>12792</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>24643</t>
+          <t>24547</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>41010</t>
+          <t>40781</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>28571</t>
+          <t>28093</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>47981</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>15329</t>
+          <t>15318</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>29819</t>
+          <t>29548</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>15132</t>
+          <t>15439</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>30191</t>
+          <t>30812</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>18486</t>
+          <t>18771</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>37838</t>
+          <t>36688</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>58543</t>
+          <t>57466</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>44521</t>
+          <t>45654</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>70491</t>
+          <t>70940</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>15505</t>
+          <t>15234</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>54518</t>
+          <t>54969</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>78721</t>
+          <t>78185</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>60978</t>
+          <t>60878</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>88740</t>
+          <t>88453</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>13318</t>
+          <t>12829</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>32990</t>
+          <t>32435</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>74654</t>
+          <t>76116</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>104905</t>
+          <t>104252</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>95620</t>
+          <t>97860</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>129898</t>
+          <t>131546</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,51%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>66571</t>
+          <t>67091</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>130893</t>
+          <t>132836</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>81201</t>
+          <t>74563</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>146685</t>
+          <t>145886</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>175584</t>
+          <t>166470</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>271184</t>
+          <t>265568</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>40193</t>
+          <t>40359</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>84095</t>
+          <t>86756</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>39672</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>75054</t>
+          <t>76410</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>93696</t>
+          <t>93814</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>152663</t>
+          <t>153738</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>95117</t>
+          <t>93354</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>184252</t>
+          <t>185631</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>111437</t>
+          <t>105325</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>196997</t>
+          <t>197531</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>241283</t>
+          <t>234198</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>370997</t>
+          <t>370082</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>293881</t>
+          <t>262555</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>548248</t>
+          <t>552170</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>278040</t>
+          <t>271860</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>502061</t>
+          <t>505511</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>681467</t>
+          <t>673776</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1033193</t>
+          <t>1029068</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,44%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>806791</t>
+          <t>799181</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1223145</t>
+          <t>1274274</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>745748</t>
+          <t>743664</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1132357</t>
+          <t>1166847</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1570647</t>
+          <t>1577862</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2192591</t>
+          <t>2209883</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>65,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41E_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6458</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12572</t>
+          <t>11650</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>9394</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13230</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14582</t>
+          <t>15851</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9814</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21710</t>
+          <t>22658</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9804</t>
+          <t>11187</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5974</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16349</t>
+          <t>18108</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5807</t>
+          <t>6150</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10682</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>15610</t>
+          <t>17337</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>10963</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22783</t>
+          <t>24797</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29876</t>
+          <t>33232</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21876</t>
+          <t>24499</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39898</t>
+          <t>44988</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19471</t>
+          <t>20848</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14134</t>
+          <t>15111</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26953</t>
+          <t>27943</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
+          <t>11,68%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>54080</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>42192</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>67484</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>9,88%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>7,71%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
           <t>12,33%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>49347</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>39859</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>60894</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83418</t>
+          <t>94488</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69993</t>
+          <t>77853</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100283</t>
+          <t>110042</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>70002</t>
+          <t>78468</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59419</t>
+          <t>65886</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81990</t>
+          <t>89496</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>153420</t>
+          <t>172956</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>135085</t>
+          <t>152080</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172342</t>
+          <t>193553</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>35,37%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>151253</t>
+          <t>162666</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>133369</t>
+          <t>144321</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>166601</t>
+          <t>181598</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>115102</t>
+          <t>124318</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102681</t>
+          <t>111318</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>128021</t>
+          <t>138503</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>266354</t>
+          <t>286984</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>245814</t>
+          <t>266626</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>286274</t>
+          <t>309726</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>56,6%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>280792</t>
+          <t>308030</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>280792</t>
+          <t>308030</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>280792</t>
+          <t>308030</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>218522</t>
+          <t>239179</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>218522</t>
+          <t>239179</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>218522</t>
+          <t>239179</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>499314</t>
+          <t>547209</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>499314</t>
+          <t>547209</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>499314</t>
+          <t>547209</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14533</t>
+          <t>15203</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8561</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22347</t>
+          <t>23420</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>9071</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13713</t>
+          <t>15252</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>22768</t>
+          <t>24275</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15846</t>
+          <t>17235</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31662</t>
+          <t>34032</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>11209</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>18850</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>14606</t>
+          <t>15916</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8710</t>
+          <t>9956</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21969</t>
+          <t>24189</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23173</t>
+          <t>25147</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15808</t>
+          <t>17697</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32481</t>
+          <t>36401</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18190</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12365</t>
+          <t>13209</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26269</t>
+          <t>27676</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>41363</t>
+          <t>44235</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32321</t>
+          <t>33141</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>53438</t>
+          <t>56292</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79976</t>
+          <t>88171</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66457</t>
+          <t>73009</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95219</t>
+          <t>103897</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>65086</t>
+          <t>73974</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53856</t>
+          <t>61947</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76669</t>
+          <t>86067</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>145062</t>
+          <t>162146</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126868</t>
+          <t>143249</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162311</t>
+          <t>181966</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>39,36%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>106633</t>
+          <t>112136</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92092</t>
+          <t>96265</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>122555</t>
+          <t>128612</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>95730</t>
+          <t>103627</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82591</t>
+          <t>91630</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>106635</t>
+          <t>116388</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>202363</t>
+          <t>215763</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>184986</t>
+          <t>195582</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>223078</t>
+          <t>234849</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>50,8%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>234668</t>
+          <t>251867</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>234668</t>
+          <t>251867</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>234668</t>
+          <t>251867</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>191493</t>
+          <t>210468</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>191493</t>
+          <t>210468</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>191493</t>
+          <t>210468</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>426161</t>
+          <t>462335</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>426161</t>
+          <t>462335</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>426161</t>
+          <t>462335</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>20443</t>
+          <t>21524</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>14865</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47302</t>
+          <t>30719</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>11897</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7018</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15846</t>
+          <t>17441</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>31233</t>
+          <t>33421</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11655</t>
+          <t>24403</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60554</t>
+          <t>43089</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11383</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>6873</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27263</t>
+          <t>19144</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1501</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>8659</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>15044</t>
+          <t>16112</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4314</t>
+          <t>10473</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31619</t>
+          <t>23503</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22147</t>
+          <t>26398</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51285</t>
+          <t>37183</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12385</t>
+          <t>13465</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>29951</t>
+          <t>34743</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>25501</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>61415</t>
+          <t>46406</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>75366</t>
+          <t>83222</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25519</t>
+          <t>67525</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>166707</t>
+          <t>99523</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>28453</t>
+          <t>31695</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22171</t>
+          <t>24765</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35481</t>
+          <t>38782</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>103819</t>
+          <t>114917</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38396</t>
+          <t>99782</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>194810</t>
+          <t>131807</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>38,69%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>344007</t>
+          <t>107673</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>197058</t>
+          <t>92858</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>430155</t>
+          <t>126276</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>29757</t>
+          <t>33786</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23056</t>
+          <t>26105</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36514</t>
+          <t>41785</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>373764</t>
+          <t>141459</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>219086</t>
+          <t>124065</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>485912</t>
+          <t>159741</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>46,89%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>473346</t>
+          <t>250904</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>473346</t>
+          <t>250904</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>473346</t>
+          <t>250904</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>80465</t>
+          <t>89749</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>80465</t>
+          <t>89749</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>80465</t>
+          <t>89749</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>553811</t>
+          <t>340652</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>553811</t>
+          <t>340652</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>553811</t>
+          <t>340652</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>33855</t>
+          <t>36577</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24391</t>
+          <t>27672</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44665</t>
+          <t>47841</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>17344</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30626</t>
+          <t>26095</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>51198</t>
+          <t>55053</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25177</t>
+          <t>44466</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>68416</t>
+          <t>68193</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>26632</t>
+          <t>28379</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>19042</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35868</t>
+          <t>38209</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>11264</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20988</t>
+          <t>18255</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>37123</t>
+          <t>39643</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>17644</t>
+          <t>30627</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52586</t>
+          <t>53921</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>48643</t>
+          <t>51483</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>37383</t>
+          <t>39342</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>62886</t>
+          <t>65945</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>30554</t>
+          <t>32507</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9751</t>
+          <t>24693</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51804</t>
+          <t>42494</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>79197</t>
+          <t>83991</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>39232</t>
+          <t>69387</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>105357</t>
+          <t>101831</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>133694</t>
+          <t>150182</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>114524</t>
+          <t>129406</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>152641</t>
+          <t>172226</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>106720</t>
+          <t>123197</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38334</t>
+          <t>105905</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>173571</t>
+          <t>138775</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>240414</t>
+          <t>273379</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>128929</t>
+          <t>247983</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>309829</t>
+          <t>302099</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>230238</t>
+          <t>253581</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>208987</t>
+          <t>233492</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>251507</t>
+          <t>277623</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>396281</t>
+          <t>210226</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>294416</t>
+          <t>192811</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>502284</t>
+          <t>228562</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>626518</t>
+          <t>463807</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>517813</t>
+          <t>433530</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>819656</t>
+          <t>492505</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>53,77%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>473062</t>
+          <t>520202</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>473062</t>
+          <t>520202</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>473062</t>
+          <t>520202</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>561389</t>
+          <t>395670</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>561389</t>
+          <t>395670</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>561389</t>
+          <t>395670</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1034451</t>
+          <t>915872</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1034451</t>
+          <t>915872</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1034451</t>
+          <t>915872</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>25917</t>
+          <t>29002</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18694</t>
+          <t>21714</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>34320</t>
+          <t>38875</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>45912</t>
+          <t>49516</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>37134</t>
+          <t>39967</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>55436</t>
+          <t>59645</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>71830</t>
+          <t>78519</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>59828</t>
+          <t>65670</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>84315</t>
+          <t>91483</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7857</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>14521</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>16677</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10382</t>
+          <t>11039</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21454</t>
+          <t>23120</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>22983</t>
+          <t>25009</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16041</t>
+          <t>18319</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31141</t>
+          <t>33840</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>16939</t>
+          <t>20366</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10926</t>
+          <t>12708</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24568</t>
+          <t>30212</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>42963</t>
+          <t>46466</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>34297</t>
+          <t>36125</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>52386</t>
+          <t>56554</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>59902</t>
+          <t>66832</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>49667</t>
+          <t>54227</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>73496</t>
+          <t>80213</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>81363</t>
+          <t>92450</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>65951</t>
+          <t>77930</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>97314</t>
+          <t>110751</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>96556</t>
+          <t>112536</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>83681</t>
+          <t>97806</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>109409</t>
+          <t>127308</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>177919</t>
+          <t>204986</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>157430</t>
+          <t>181532</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>197666</t>
+          <t>228768</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>36,26%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>93494</t>
+          <t>104356</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>77130</t>
+          <t>86565</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>110748</t>
+          <t>122633</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>137919</t>
+          <t>151157</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>121765</t>
+          <t>135330</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>151235</t>
+          <t>167894</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>231413</t>
+          <t>255512</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>210499</t>
+          <t>232790</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>254311</t>
+          <t>282082</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>225570</t>
+          <t>254506</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>225570</t>
+          <t>254506</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>225570</t>
+          <t>254506</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>338476</t>
+          <t>376352</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>338476</t>
+          <t>376352</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>338476</t>
+          <t>376352</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>564046</t>
+          <t>630858</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>564046</t>
+          <t>630858</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>564046</t>
+          <t>630858</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12792</t>
+          <t>10777</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>32266</t>
+          <t>35540</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>24547</t>
+          <t>27144</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>40781</t>
+          <t>45461</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>37074</t>
+          <t>39609</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>28093</t>
+          <t>30462</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>47981</t>
+          <t>50489</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4258,12 +4258,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>21081</t>
+          <t>23921</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>15318</t>
+          <t>17131</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>29548</t>
+          <t>33382</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>22089</t>
+          <t>25066</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>15439</t>
+          <t>17548</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>30812</t>
+          <t>34289</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>10192</t>
+          <t>10337</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>18771</t>
+          <t>18712</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>46775</t>
+          <t>51334</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>36688</t>
+          <t>41196</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>57466</t>
+          <t>63886</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>56967</t>
+          <t>61671</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>45654</t>
+          <t>48447</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>70940</t>
+          <t>75916</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>15234</t>
+          <t>15540</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>65902</t>
+          <t>72165</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>54969</t>
+          <t>60354</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>78185</t>
+          <t>85615</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>73232</t>
+          <t>79926</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>60878</t>
+          <t>65736</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>88453</t>
+          <t>94627</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>22600</t>
+          <t>22036</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>12829</t>
+          <t>12291</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>32435</t>
+          <t>30861</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>90382</t>
+          <t>96603</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>76116</t>
+          <t>82264</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>104252</t>
+          <t>112189</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>112983</t>
+          <t>118638</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>97860</t>
+          <t>101232</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>131546</t>
+          <t>136845</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>42,12%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>45938</t>
+          <t>45349</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>45938</t>
+          <t>45349</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>45938</t>
+          <t>45349</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>256407</t>
+          <t>279562</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>256407</t>
+          <t>279562</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>256407</t>
+          <t>279562</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>302345</t>
+          <t>324911</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>302345</t>
+          <t>324911</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>302345</t>
+          <t>324911</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,102 +4817,102 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>105997</t>
+          <t>112833</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>67091</t>
+          <t>96471</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>132836</t>
+          <t>134440</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
+          <t>8,24%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>133895</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>117653</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>151255</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>8,42%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>7,39%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>9,51%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>246728</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>222132</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>272091</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
           <t>7,66%</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>122688</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>74563</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>145886</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>7,45%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>8,86%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>228685</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>166470</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>265568</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>67036</t>
+          <t>72339</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>40359</t>
+          <t>59063</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>86756</t>
+          <t>87765</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>60419</t>
+          <t>66744</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>39672</t>
+          <t>55088</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>76410</t>
+          <t>81487</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>127455</t>
+          <t>139083</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>93814</t>
+          <t>120658</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>153738</t>
+          <t>160808</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>150971</t>
+          <t>166963</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>93354</t>
+          <t>143695</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>185631</t>
+          <t>192737</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>165756</t>
+          <t>178589</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>105325</t>
+          <t>158655</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>197531</t>
+          <t>200375</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>316727</t>
+          <t>345552</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>234198</t>
+          <t>311314</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>370082</t>
+          <t>377204</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>461148</t>
+          <t>516274</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>262555</t>
+          <t>478351</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>552170</t>
+          <t>555124</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>432718</t>
+          <t>492035</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>271860</t>
+          <t>461841</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>505511</t>
+          <t>525421</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>893867</t>
+          <t>1008310</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>673776</t>
+          <t>961271</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1029068</t>
+          <t>1055640</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>948224</t>
+          <t>762447</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>799181</t>
+          <t>717081</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1274274</t>
+          <t>806157</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>865170</t>
+          <t>719717</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>743664</t>
+          <t>686380</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1166847</t>
+          <t>754527</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1813394</t>
+          <t>1482164</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1577862</t>
+          <t>1429595</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2209883</t>
+          <t>1536971</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>47,7%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1733376</t>
+          <t>1630857</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1733376</t>
+          <t>1630857</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1733376</t>
+          <t>1630857</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>1646752</t>
+          <t>1590980</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1646752</t>
+          <t>1590980</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1646752</t>
+          <t>1590980</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>3380128</t>
+          <t>3221837</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>3380128</t>
+          <t>3221837</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3380128</t>
+          <t>3221837</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">

--- a/data/trans_orig/P41E_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023 (tasa de respuesta: 69,32%)</t>
+          <t>Población según su nivel de acuerdo sobre la satisfacción de sus relaciones sexuales por ambas partes en el último mes en 2023 (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
